--- a/docs/all/01_TablasDescriptivas/idx7_gini_summary_labels.xlsx
+++ b/docs/all/01_TablasDescriptivas/idx7_gini_summary_labels.xlsx
@@ -409,7 +409,7 @@
         <v>-0.4592497601725889</v>
       </c>
       <c r="E2">
-        <v>0.06289475801223222</v>
+        <v>0.06289475801223221</v>
       </c>
       <c r="F2">
         <v>-0.667980058203487</v>
